--- a/95 Файлы/Допуск. Концертный комплекс/Допуск. Концертный комплекс. Европейские технологии.xlsx
+++ b/95 Файлы/Допуск. Концертный комплекс/Допуск. Концертный комплекс. Европейские технологии.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\habarov.db\Documents\16.Концертный зал\01. Допуск\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\habarov.db\Documents\__Для Обсидиан\vault_second_brain\95 Файлы\Допуск. Концертный комплекс\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="97">
   <si>
     <t>Фамилия</t>
   </si>
@@ -194,21 +194,9 @@
     <t>Рук-ль группы</t>
   </si>
   <si>
-    <t xml:space="preserve">Линев </t>
-  </si>
-  <si>
-    <t>Андрей</t>
-  </si>
-  <si>
-    <t>с 1.12.2025 по 31.12.2025</t>
-  </si>
-  <si>
     <t>Место рождения</t>
   </si>
   <si>
-    <t>Адрес регестрации</t>
-  </si>
-  <si>
     <t>г. Сочи</t>
   </si>
   <si>
@@ -269,19 +257,73 @@
     <t>Р. Пос. Новоспасское, Новоспасского района, Ульяновской области</t>
   </si>
   <si>
-    <t>Адлерский район, г. Сочи, Краснодарского края</t>
-  </si>
-  <si>
     <t>г. Санкт-Петербург, ул. Адмирала Трибуца 7-137</t>
   </si>
   <si>
     <t>Краснодарский край, г.Сочи, Адлерский район, ул. Лесная д.10</t>
   </si>
   <si>
-    <t>Краснодарский край, г.Сочи, Адлерский район, ул. Ивановская д. 4А, кв.17</t>
-  </si>
-  <si>
     <t>№11/25-10931/19 от 5.11.2025</t>
+  </si>
+  <si>
+    <t>Адрес регистрации</t>
+  </si>
+  <si>
+    <t>Михалев</t>
+  </si>
+  <si>
+    <t>Антон</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> г. Сочи, Краснодарского края</t>
+  </si>
+  <si>
+    <t>Краснодарский край, г.Сочи, с Краевско-армянское, ул. Саят-Нова, д.57</t>
+  </si>
+  <si>
+    <t>Специалист</t>
+  </si>
+  <si>
+    <t>Богданов</t>
+  </si>
+  <si>
+    <t>Геннадий</t>
+  </si>
+  <si>
+    <t>Стефанович</t>
+  </si>
+  <si>
+    <t>ст. Отрадная, Отрадненского р-на, Краснодарского края</t>
+  </si>
+  <si>
+    <t>г. Сочи, ул. Красноармейская 7кА, кв 8. 22.05.1996г</t>
+  </si>
+  <si>
+    <t>Родин</t>
+  </si>
+  <si>
+    <t>Федорович</t>
+  </si>
+  <si>
+    <t>ст Бородулино, Верещагинского района Пермоской области</t>
+  </si>
+  <si>
+    <t>г.Сочи, Хостинский район, ул. Шоссейная д. 7А, кв 49</t>
+  </si>
+  <si>
+    <t>Клинков</t>
+  </si>
+  <si>
+    <t>Максимович</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> с.Армизонское, Армизонского р-на, Тюменской обл.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тюменская обл., г. Тюмень, ул. 30 лет Победы, д. 76, кв. 194 </t>
+  </si>
+  <si>
+    <t>с 01.05.2026 по 31.05.2026</t>
   </si>
 </sst>
 </file>
@@ -351,7 +393,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -403,13 +445,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyBorder="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -440,6 +495,17 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -758,7 +824,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:I28"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.140625" style="1" customWidth="1"/>
@@ -773,16 +839,16 @@
   <sheetData>
     <row r="1" spans="2:9" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:9" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
     </row>
     <row r="3" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
@@ -790,13 +856,13 @@
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
     </row>
     <row r="4" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
@@ -804,11 +870,11 @@
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
     </row>
     <row r="5" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
@@ -816,13 +882,13 @@
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
-      <c r="E5" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="F5" s="22"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="22"/>
-      <c r="I5" s="22"/>
+      <c r="E5" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="F5" s="27"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="27"/>
+      <c r="I5" s="27"/>
     </row>
     <row r="6" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
@@ -830,13 +896,13 @@
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="22"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="27"/>
     </row>
     <row r="7" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
@@ -844,13 +910,13 @@
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
-      <c r="E7" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="F7" s="22"/>
-      <c r="G7" s="22"/>
-      <c r="H7" s="22"/>
-      <c r="I7" s="22"/>
+      <c r="E7" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="27"/>
     </row>
     <row r="8" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
@@ -858,39 +924,39 @@
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="22"/>
-      <c r="I8" s="22"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="27"/>
+      <c r="I8" s="27"/>
     </row>
     <row r="9" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="22" t="s">
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="22"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="27"/>
     </row>
     <row r="10" spans="2:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="3"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
     </row>
     <row r="11" spans="2:9" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="5" t="s">
@@ -909,10 +975,10 @@
         <v>16</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>3</v>
@@ -935,10 +1001,10 @@
         <v>30718</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>39</v>
@@ -961,10 +1027,10 @@
         <v>31515</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="I13" s="7" t="s">
         <v>39</v>
@@ -987,10 +1053,10 @@
         <v>29409</v>
       </c>
       <c r="G14" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="H14" s="10" t="s">
         <v>58</v>
-      </c>
-      <c r="H14" s="10" t="s">
-        <v>62</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>39</v>
@@ -1013,10 +1079,10 @@
         <v>30152</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I15" s="7" t="s">
         <v>39</v>
@@ -1039,16 +1105,16 @@
         <v>28130</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="11">
         <v>6</v>
       </c>
@@ -1065,42 +1131,42 @@
         <v>27805</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="I17" s="7" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="2:9" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="11">
         <v>7</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F18" s="10">
         <v>32507</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="I18" s="7" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="2:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="11">
         <v>8</v>
       </c>
@@ -1117,16 +1183,16 @@
         <v>27337</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I19" s="7" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="2:9" ht="162" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="162" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="11">
         <v>9</v>
       </c>
@@ -1143,16 +1209,16 @@
         <v>32142</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="I20" s="7" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="2:9" ht="119.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="119.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="11">
         <v>10</v>
       </c>
@@ -1169,115 +1235,195 @@
         <v>30573</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="I21" s="7" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="2:9" ht="138.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="138.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="11">
         <v>11</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F22" s="8">
-        <v>29739</v>
+        <v>32716</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H22" s="8" t="s">
         <v>81</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="23" spans="2:9" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="138.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="12">
+        <v>12</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="F23" s="14">
+        <v>23345</v>
+      </c>
+      <c r="G23" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="H23" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="I23" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="138.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="15"/>
+      <c r="B24" s="11">
+        <v>13</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="F24" s="8">
+        <v>24788</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="138.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="16"/>
+      <c r="B25" s="11">
+        <v>14</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F25" s="8">
+        <v>33712</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="18" t="s">
         <v>23</v>
-      </c>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
-    </row>
-    <row r="24" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-    </row>
-    <row r="25" spans="2:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
-    </row>
-    <row r="26" spans="2:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="18" t="s">
-        <v>7</v>
       </c>
       <c r="C26" s="18"/>
       <c r="D26" s="18"/>
       <c r="E26" s="18"/>
-      <c r="F26" s="16" t="s">
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
+    </row>
+    <row r="27" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
+    </row>
+    <row r="28" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+    </row>
+    <row r="29" spans="1:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="23"/>
+      <c r="D29" s="23"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="16"/>
-    </row>
-    <row r="27" spans="2:9" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B27" s="19">
+      <c r="G29" s="21"/>
+      <c r="H29" s="21"/>
+      <c r="I29" s="21"/>
+    </row>
+    <row r="30" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B30" s="24">
         <f ca="1">TODAY()</f>
-        <v>45993</v>
-      </c>
-      <c r="C27" s="19"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-    </row>
-    <row r="28" spans="2:9" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B28" s="14" t="s">
+        <v>46140</v>
+      </c>
+      <c r="C30" s="24"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+    </row>
+    <row r="31" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B31" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C28" s="14"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -1291,13 +1437,13 @@
     <mergeCell ref="E8:I8"/>
     <mergeCell ref="E9:I9"/>
     <mergeCell ref="E10:I10"/>
-    <mergeCell ref="B23:I23"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B26:I26"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="F28:I28"/>
+    <mergeCell ref="F29:I29"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.31496062992125984" right="0.31496062992125984" top="0.55118110236220474" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="82" fitToHeight="0" orientation="portrait" r:id="rId1"/>
